--- a/spectral_slope/プログラムディストーション複合音単音.xlsx
+++ b/spectral_slope/プログラムディストーション複合音単音.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_slope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14E5D8D-CBA8-4B31-B2A4-08DCBC383A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D7F863-BFA3-4255-B50B-485A0681869D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E21523D0-F10C-4256-AFA2-087A89E57FC7}"/>
+    <workbookView xWindow="6600" yWindow="1275" windowWidth="21600" windowHeight="11295" xr2:uid="{E21523D0-F10C-4256-AFA2-087A89E57FC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
